--- a/光伏配储项目/电价数据/2026/康乐站.xlsx
+++ b/光伏配储项目/电价数据/2026/康乐站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5118</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75852</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5749</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5995900000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51793</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51646</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45452</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44547</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44464</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12845</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10449</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11886</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10841</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13109</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04913</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10813</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.15771</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.19773</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.26896</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09132</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.25503</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10124</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04448</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15252</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21675</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25512</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2397</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.17591</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.02173</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.51661</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14315</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28361</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21296</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.64249</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5598200000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.56659</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.3356</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.61726</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46149</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44675</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.46106</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57808</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.63598</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8214900000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6399600000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.65266</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.79559</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.15536</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68592</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6005499999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.8241499999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.66462</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.6800900000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6515599999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6214500000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47754</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42612</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70813</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.80337</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.55199</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8655</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5364500000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51806</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50501</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50889</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48728</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46936</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49786</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5998600000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7523500000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42835</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44144</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43243</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5216900000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17159</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06186999999999999</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5031600000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.76749</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.17357</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.79796</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5392100000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.51461</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.26597</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.08845</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.40025</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24686</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.43233</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.64106</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7865700000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.6228400000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.20922</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79008</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.73975</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.66683</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.60551</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77462</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.5694900000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.45574</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.08082</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47068</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6755</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43689</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33469</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5254800000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43703</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47376</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45354</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.46361</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.48087</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47629</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40724</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.50896</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48661</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16415</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52396</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42961</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.18009</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.52749</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.57716</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.8855599999999999</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56388</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6398400000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.71154</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5770599999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.49757</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44353</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.52724</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42497</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.48408</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45165</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.45905</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44091</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41837</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41022</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34232</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.28067</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.32728</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.21437</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.44717</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.09792000000000001</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.09783</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17439</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.17908</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.21982</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.51209</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06737</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.12036</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.22931</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.24328</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28542</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21685</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23657</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20043</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26495</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12479</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.16635</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.26871</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6714199999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47225</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.42759</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.2992</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25903</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04787</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03902000000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04878</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04989</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04452</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04089</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04555</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03619</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04715</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04625</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04754</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04633</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04665</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04467</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04709000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04201</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21832</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.03943</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04531</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05511</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04787</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00314</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.01306</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15552</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05565</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11312</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41114</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35061</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6771900000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44472</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10256</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04372</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04543</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04671</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09801</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00463</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04499</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04462</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04954</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04775</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19998</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14286</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33537</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31746</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27124</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17242</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15867</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17096</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14773</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15946</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15861</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23617</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21403</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22658</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27173</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42872</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45701</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15635</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909400000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78108</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92052</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91527</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86537</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29797</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89042</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6322300000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87019</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53927</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33377</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03495</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53366</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7933600000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5293600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77538</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77944</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87707</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8751100000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49538</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40282</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45252</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20992</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62475</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53907</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49856</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45622</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5956</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60148</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6617799999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47371</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58231</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45178</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8781599999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.62817</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87526</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.85782</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8651599999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44303</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46102</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41191</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45139</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35325</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9154600000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46348</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49873</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16655</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26262</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19898</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19064</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27585</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43147</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44755</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59454</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88976</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.32763</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13612</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69728</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78727</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64279</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57645</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44965</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49961</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4392200000000001</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42253</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49864</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43343</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43343</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42667</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44883</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39579</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42291</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43272</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42217</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49187</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.96329</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6184400000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.21116</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.1749</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25038</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.00547</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6997100000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.67989</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.40761</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.43835</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.46334</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>1.35106</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5747599999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46137</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7435</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46331</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43625</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41919</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32328</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.39076</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.91689</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16381</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.16839</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.12285</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17528</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.96975</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.95978</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14988</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15008</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.15705</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28823</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.19847</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.15726</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16244</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>1.31872</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44766</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4392200000000001</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43702</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44306</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34819</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53515</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4663</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27201</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20328</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25026</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24383</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24246</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24473</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35962</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.49312</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.13796</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24932</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.26038</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42947</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44209</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7001499999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5273099999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28254</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.31567</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34938</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41122</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65651</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.76702</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45174</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45688</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34426</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.23029</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20011</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28042</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26957</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27991</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.19866</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.48467</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.46288</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.49576</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.47917</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42133</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64163</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6077400000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5938600000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46487</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.66611</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47055</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8229</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47944</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.65342</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47518</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42941</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41862</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35967</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48896</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5365800000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48482</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49181</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39709</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55698</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44863</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.7069800000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44983</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46833</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44741</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.4676</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45946</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.65119</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.37295</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41757</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43949</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49236</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43892</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50851</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51189</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5461699999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69857</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.73017</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.49652</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.6503099999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8102200000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59068</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5264</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8379</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77759</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6274400000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67713</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47779</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48351</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47614</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46988</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55564</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42898</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44108</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45561</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45445</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20726</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04323</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46122</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11415</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18001</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29683</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43226</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36456</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22547</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23058</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25011</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25032</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04292</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17114</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18324</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.2299</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25093</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26619</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23374</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27623</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34907</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.3257</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1.33697</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.24816</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23321</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16067</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.19863</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03222999999999999</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04904</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10999</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.02073</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03902000000000001</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01234</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03623</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03247</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04714</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02421</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02169</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.20183</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04909</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.0009300000000000001</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04909</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03484</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04905</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.0488</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.18936</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23032</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28037</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.25912</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26085</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25651</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28264</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41057</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.27702</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.11455</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.55398</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.13407</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.26772</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.24563</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.25837</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23496</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22277</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25255</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.2425</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.20553</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23056</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23559</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27201</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25752</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.25603</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.2372</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26319</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21235</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.13135</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.61936</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.58805</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6330800000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5706100000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.14811</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.30592</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>1.11979</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1.23261</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.17368</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.09733</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.05724</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22334</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.09067</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16392</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02892</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.09943</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13002</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02638</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.09237000000000001</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.13666</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1.25893</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.33327</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1.33309</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>1.32862</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.33863</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.35893</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.37509</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.33757</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.38786</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.37766</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.45028</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.37368</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.37484</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.36214</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.3634</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.35461</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.36995</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.35811</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.3676</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32276</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.35442</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.37143</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.55287</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.55045</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.3669</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.48406</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.39281</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44693</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14248</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27899</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27024</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27399</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50615</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32843</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27618</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.64424</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.60329</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.34952</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5062</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26339</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49349</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50399</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46729</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48995</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42416</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.58051</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.48851</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45781</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36829</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48088</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40134</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.46258</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27694</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.44971</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.43261</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41133</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43657</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51422</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58489</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5894199999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5190399999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.50918</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.54944</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4660899999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5120800000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7319600000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.89636</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.59109</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.58924</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37458</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37289</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25387</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.21969</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17012</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.15371</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07287</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.21172</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04262</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21166</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16952</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01121</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26497</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16642</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06311</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06166</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07906000000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.16865</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08465</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06128</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17588</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15717</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24171</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43464</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35683</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.86239</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.4670899999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.25252</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.24721</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27016</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24348</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11351</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.08585</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.09178</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.12601</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.15728</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00357</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01951</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04924</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02088</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02702</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.08857</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.22275</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04913</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23601</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.007059999999999999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.21117</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.50069</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5873999999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3582</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.62253</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45696</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.22821</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14281</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.2035</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22704</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.22832</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00265</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04729</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04740999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04678</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04759</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04744</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04187</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07790000000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06272</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.16822</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19343</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.11922</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25085</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12284</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05565</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14442</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11635</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23491</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18269</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23296</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24024</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20107</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24138</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3643</v>
       </c>
     </row>
   </sheetData>
